--- a/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRBE398RT4DW1DRFHPA8VBH9</t>
+          <t>h_01KRDDN0K3BVX2YPFTQWQAVVN1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRBE398RT4DW1DRFHPA8VBH9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3BVX2YPFTQWQAVVN1</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRBE398RFT0C8PAAQE6C3B0V</t>
+          <t>h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRBE398RFT0C8PAAQE6C3B0V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,63 +803,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Users Management</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Manage System Users</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Source Filter Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EHRYTAC6GARWBPXWK</t>
+          <t>h_01KRDDN0K4JZR988KPM3ZGD21D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EHRYTAC6GARWBPXWK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4JZR988KPM3ZGD21D</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EZXHZKE1TQS5K186B</t>
+          <t>h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EZXHZKE1TQS5K186B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification Template</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,85 +1001,85 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Notification Template</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EntraID to D365 Employees</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Entra Users to D365 Users</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,76 +1133,142 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>EntraID to D365 Employees</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Entra Users to D365 Users</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
@@ -991,7 +991,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Template</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Notification Template</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>

--- a/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Template</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,208 +1067,340 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Template</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EntraID to D365 Employees</t>
+          <t>Create Notification</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Entra Users to D365 Users</t>
+          <t>Update Notification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Deactivate Notification</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UKG Ready to D365 Employees</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UKG Ready System Users to D365 Users</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>h_01KTR42Z3HG45RC5309YVERJ5S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTR42Z3HG45RC5309YVERJ5S</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K3FM9KRV3N42DTA00G</t>
+          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3FM9KRV3N42DTA00G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K435R6MCNKX39TEX8B</t>
+          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K435R6MCNKX39TEX8B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manage System Users</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Manage System Users</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K4JZR988KPM3ZGD21D</t>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4JZR988KPM3ZGD21D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
+          <t>h_01KRDDN0K4JZR988KPM3ZGD21D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4JZR988KPM3ZGD21D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
+          <t>h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
+          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,41 +1023,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notification Template</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Create Notification</t>
+          <t>Notification Template</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQVSTC8WW591B03TGBN</t>
+          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVSTC8WW591B03TGBN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Update Notification</t>
+          <t>Create Notification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQVXZ0NEHWR02TY477D</t>
+          <t>h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVXZ0NEHWR02TY477D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deactivate Notification</t>
+          <t>Update Notification</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,41 +1199,41 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
+          <t>h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Deactivate Notification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,63 +1243,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UKG Ready to D365 Employees</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UKG Ready System Users to D365 Users</t>
+          <t>UKG Ready to D365 Employees</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,41 +1309,41 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>UKG Ready System Users to D365 Users</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,54 +1353,76 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
+++ b/site/Dynamics365-ERP-UKG-Ready-Integration-Guide/headings.xlsx
@@ -661,51 +661,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synchronization Settings</t>
+          <t>Manage Employees</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K3BVX2YPFTQWQAVVN1</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3BVX2YPFTQWQAVVN1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Employees</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>h_01KTRHH5YRWSCWSDSHJENEEV24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVSS2AZXF2B8AGHB5E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRHH5YRWSCWSDSHJENEEV24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KTR42Z3HG45RC5309YVERJ5S</t>
+          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTR42Z3HG45RC5309YVERJ5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVZTAQ5FH2VMSSCEZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNMP7V37BGNDT0PQTYGM99V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3FM9KRV3N42DTA00G</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K3FM9KRV3N42DTA00G</t>
+          <t>h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K3FM9KRV3N42DTA00G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K435R6MCNKX39TEX8B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Manage System Users</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K435R6MCNKX39TEX8B</t>
+          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K435R6MCNKX39TEX8B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Manage System Users</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KKBMXVHB7WJDCHSC4ACBW4XT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>h_01KTRHH5YRHPAJVREYED2A3F8E</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JVFMC64ERZV9VCKCEH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRHH5YRHPAJVREYED2A3F8E</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K4JZR988KPM3ZGD21D</t>
+          <t>h_01KTRHH5YRPDJQDT9S0BZANHTN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4JZR988KPM3ZGD21D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRHH5YRPDJQDT9S0BZANHTN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
+          <t>h_01KTRHH5YRFMWC0SS48Z26YWYB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K4KCJ1YASRR4RTGEKW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRHH5YRFMWC0SS48Z26YWYB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
+          <t>h_01KTRH6H3WR2KHPNCG3GSC3H41</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K40GDGYNDSE8XBEEM0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRH6H3WR2KHPNCG3GSC3H41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>h_01KTRH7JAN22KAS6PGPQRVTK3D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KHNR86JV4CP6MH76CAPA1ZH4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRH7JAN22KAS6PGPQRVTK3D</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Safeguard Limits</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
+          <t>h_01KTRH8RKPVBSH08ZE1N3AXFXZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRDDN0K41GSHEXCRHD1YZQ30</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRH8RKPVBSH08ZE1N3AXFXZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,63 +1045,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KTRHH5YSBTAAPEBFQ5C8JD1Y</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KTRHH5YSBTAAPEBFQ5C8JD1Y</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notification Template</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KJCSZ76EG6G02NECNPM0QZ80</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Create Notification</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQVSTC8WW591B03TGBN</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVSTC8WW591B03TGBN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Update Notification</t>
+          <t>Create Notification</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQVXZ0NEHWR02TY477D</t>
+          <t>h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVXZ0NEHWR02TY477D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVSTC8WW591B03TGBN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deactivate Notification</t>
+          <t>Update Notification</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
+          <t>h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQVXZ0NEHWR02TY477D</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Deactivate Notification</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dynamics365-ERP-UKG-Ready-Integration-Guide/#h_01KRE0VPQV0PHSHTB4AZR8EYNV</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UKG Ready to D365 Employees</t>
+          <t>Employees Mapper</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UKG Ready System Users to D365 Users</t>
+          <t>Users Mapper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
